--- a/LTL_qty.xlsx
+++ b/LTL_qty.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11008"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/giovannighedini/Desktop/ATLAS/AI_Automation/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://acusa-my.sharepoint.com/personal/g_ghedini_atlasconcordeusa_com/Documents/Desktop/AI - Automations/BOL creation/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6BF367BB-19BC-0C49-AFDB-25423D3B18D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="74" documentId="8_{41BA2822-1FC3-424A-BF5C-A2447EBC91C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7E4EAC45-105B-45C1-8560-DACF3689519A}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="620" windowWidth="28800" windowHeight="16200" xr2:uid="{B388D9E8-F042-4987-BDB7-8E3EC1CFA04A}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{B388D9E8-F042-4987-BDB7-8E3EC1CFA04A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1195,14 +1195,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F30446A3-A986-4686-A765-4C12AB9F4FB1}">
   <dimension ref="A1:E126"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="15.6640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="72" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="13" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="18" t="s">
         <v>28</v>
       </c>
@@ -1219,7 +1219,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>29</v>
       </c>
@@ -1236,7 +1236,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>29</v>
       </c>
@@ -1253,7 +1253,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>29</v>
       </c>
@@ -1270,12 +1270,12 @@
         <v>84</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>29</v>
       </c>
       <c r="B5" s="2">
-        <v>610010002399</v>
+        <v>610010005234</v>
       </c>
       <c r="C5" s="4" t="s">
         <v>4</v>
@@ -1287,7 +1287,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>29</v>
       </c>
@@ -1301,7 +1301,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>29</v>
       </c>
@@ -1318,12 +1318,12 @@
         <v>84</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>29</v>
       </c>
       <c r="B8" s="2">
-        <v>610010004701</v>
+        <v>610010005236</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>6</v>
@@ -1335,7 +1335,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>29</v>
       </c>
@@ -1349,7 +1349,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>29</v>
       </c>
@@ -1366,7 +1366,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>29</v>
       </c>
@@ -1383,7 +1383,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>29</v>
       </c>
@@ -1400,7 +1400,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>29</v>
       </c>
@@ -1414,7 +1414,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>29</v>
       </c>
@@ -1431,7 +1431,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>29</v>
       </c>
@@ -1448,7 +1448,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>29</v>
       </c>
@@ -1462,7 +1462,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>29</v>
       </c>
@@ -1479,7 +1479,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>29</v>
       </c>
@@ -1493,7 +1493,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>29</v>
       </c>
@@ -1510,7 +1510,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>29</v>
       </c>
@@ -1527,7 +1527,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>29</v>
       </c>
@@ -1544,7 +1544,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>29</v>
       </c>
@@ -1561,7 +1561,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>29</v>
       </c>
@@ -1578,7 +1578,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>29</v>
       </c>
@@ -1595,7 +1595,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>29</v>
       </c>
@@ -1612,7 +1612,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>29</v>
       </c>
@@ -1629,7 +1629,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>29</v>
       </c>
@@ -1646,7 +1646,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>29</v>
       </c>
@@ -1663,7 +1663,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>29</v>
       </c>
@@ -1680,7 +1680,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>29</v>
       </c>
@@ -1697,7 +1697,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>29</v>
       </c>
@@ -1714,7 +1714,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>29</v>
       </c>
@@ -1731,7 +1731,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>29</v>
       </c>
@@ -1745,7 +1745,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>29</v>
       </c>
@@ -1762,7 +1762,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>29</v>
       </c>
@@ -1779,7 +1779,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>29</v>
       </c>
@@ -1793,7 +1793,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>29</v>
       </c>
@@ -1810,7 +1810,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>29</v>
       </c>
@@ -1827,7 +1827,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>29</v>
       </c>
@@ -1841,7 +1841,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>29</v>
       </c>
@@ -1858,7 +1858,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>29</v>
       </c>
@@ -1875,7 +1875,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>29</v>
       </c>
@@ -1889,7 +1889,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>29</v>
       </c>
@@ -1906,7 +1906,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>29</v>
       </c>
@@ -1920,7 +1920,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>29</v>
       </c>
@@ -1937,7 +1937,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="46" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>29</v>
       </c>
@@ -1954,7 +1954,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>29</v>
       </c>
@@ -1968,7 +1968,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>29</v>
       </c>
@@ -1985,7 +1985,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>29</v>
       </c>
@@ -1999,7 +1999,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>29</v>
       </c>
@@ -2016,7 +2016,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>29</v>
       </c>
@@ -2030,7 +2030,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>29</v>
       </c>
@@ -2047,7 +2047,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>29</v>
       </c>
@@ -2061,7 +2061,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>29</v>
       </c>
@@ -2078,7 +2078,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>29</v>
       </c>
@@ -2095,7 +2095,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>29</v>
       </c>
@@ -2109,7 +2109,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>29</v>
       </c>
@@ -2126,7 +2126,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>29</v>
       </c>
@@ -2143,7 +2143,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>29</v>
       </c>
@@ -2157,7 +2157,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>29</v>
       </c>
@@ -2174,7 +2174,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>29</v>
       </c>
@@ -2191,7 +2191,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>29</v>
       </c>
@@ -2205,7 +2205,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>29</v>
       </c>
@@ -2222,7 +2222,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>29</v>
       </c>
@@ -2239,7 +2239,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>29</v>
       </c>
@@ -2253,7 +2253,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>29</v>
       </c>
@@ -2270,7 +2270,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>29</v>
       </c>
@@ -2287,7 +2287,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>29</v>
       </c>
@@ -2301,7 +2301,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="69" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>29</v>
       </c>
@@ -2314,11 +2314,11 @@
       <c r="D69">
         <v>16</v>
       </c>
-      <c r="E69">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="E69" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>29</v>
       </c>
@@ -2331,11 +2331,11 @@
       <c r="D70">
         <v>16</v>
       </c>
-      <c r="E70">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="71" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="E70" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>29</v>
       </c>
@@ -2348,11 +2348,11 @@
       <c r="D71">
         <v>16</v>
       </c>
-      <c r="E71">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="72" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="E71" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>29</v>
       </c>
@@ -2365,11 +2365,11 @@
       <c r="D72">
         <v>16</v>
       </c>
-      <c r="E72">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="73" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="E72" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>29</v>
       </c>
@@ -2382,11 +2382,11 @@
       <c r="D73">
         <v>16</v>
       </c>
-      <c r="E73">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="E73" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>29</v>
       </c>
@@ -2403,7 +2403,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>29</v>
       </c>
@@ -2420,7 +2420,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>29</v>
       </c>
@@ -2437,7 +2437,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>29</v>
       </c>
@@ -2454,7 +2454,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>29</v>
       </c>
@@ -2471,7 +2471,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>29</v>
       </c>
@@ -2488,7 +2488,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>29</v>
       </c>
@@ -2505,7 +2505,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>29</v>
       </c>
@@ -2522,7 +2522,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>29</v>
       </c>
@@ -2539,7 +2539,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>29</v>
       </c>
@@ -2556,7 +2556,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>29</v>
       </c>
@@ -2573,7 +2573,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>29</v>
       </c>
@@ -2590,7 +2590,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
         <v>29</v>
       </c>
@@ -2607,7 +2607,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>29</v>
       </c>
@@ -2624,7 +2624,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
         <v>29</v>
       </c>
@@ -2641,7 +2641,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="89" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
         <v>29</v>
       </c>
@@ -2658,7 +2658,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>29</v>
       </c>
@@ -2675,7 +2675,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="91" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
         <v>29</v>
       </c>
@@ -2692,7 +2692,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>29</v>
       </c>
@@ -2709,7 +2709,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
         <v>29</v>
       </c>
@@ -2726,7 +2726,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
         <v>29</v>
       </c>
@@ -2743,7 +2743,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
         <v>29</v>
       </c>
@@ -2760,7 +2760,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="96" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
         <v>29</v>
       </c>
@@ -2777,7 +2777,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
         <v>29</v>
       </c>
@@ -2794,7 +2794,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
         <v>30</v>
       </c>
@@ -2811,7 +2811,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
         <v>30</v>
       </c>
@@ -2828,7 +2828,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="100" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
         <v>30</v>
       </c>
@@ -2845,7 +2845,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="101" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
         <v>30</v>
       </c>
@@ -2862,7 +2862,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="102" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
         <v>30</v>
       </c>
@@ -2879,7 +2879,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="103" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
         <v>30</v>
       </c>
@@ -2896,7 +2896,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="104" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
         <v>30</v>
       </c>
@@ -2913,7 +2913,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="105" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
         <v>30</v>
       </c>
@@ -2930,7 +2930,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="106" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
         <v>30</v>
       </c>
@@ -2947,7 +2947,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="107" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
         <v>30</v>
       </c>
@@ -2964,7 +2964,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="108" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
         <v>30</v>
       </c>
@@ -2981,7 +2981,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="109" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
         <v>30</v>
       </c>
@@ -2998,7 +2998,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="110" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
         <v>30</v>
       </c>
@@ -3015,7 +3015,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="111" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
         <v>30</v>
       </c>
@@ -3032,7 +3032,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="112" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
         <v>30</v>
       </c>
@@ -3049,7 +3049,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="113" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
         <v>30</v>
       </c>
@@ -3066,7 +3066,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="114" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
         <v>30</v>
       </c>
@@ -3083,7 +3083,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="115" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
         <v>30</v>
       </c>
@@ -3100,7 +3100,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="116" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
         <v>30</v>
       </c>
@@ -3117,7 +3117,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="117" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
         <v>30</v>
       </c>
@@ -3134,7 +3134,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="118" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
         <v>30</v>
       </c>
@@ -3151,7 +3151,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="119" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
         <v>30</v>
       </c>
@@ -3168,7 +3168,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="120" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
         <v>30</v>
       </c>
@@ -3185,7 +3185,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="121" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
         <v>30</v>
       </c>
@@ -3202,7 +3202,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="122" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
         <v>30</v>
       </c>
@@ -3219,7 +3219,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="123" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
         <v>30</v>
       </c>
@@ -3236,7 +3236,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="124" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
         <v>30</v>
       </c>
@@ -3253,7 +3253,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="125" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
         <v>30</v>
       </c>
@@ -3270,7 +3270,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="126" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
         <v>30</v>
       </c>
